--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.40555454722855</v>
+        <v>8.35340261392464</v>
       </c>
       <c r="D2" t="n">
-        <v>50.06284860222439</v>
+        <v>8.135212897861464</v>
       </c>
       <c r="E2" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F2" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.55729060409859</v>
+        <v>7.240559723166021</v>
       </c>
       <c r="D3" t="n">
-        <v>46.41042197278974</v>
+        <v>7.541693570578333</v>
       </c>
       <c r="E3" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F3" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.20219384253871</v>
+        <v>7.182856499412541</v>
       </c>
       <c r="D4" t="n">
-        <v>45.5877410914316</v>
+        <v>7.408007927357636</v>
       </c>
       <c r="E4" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F4" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.71198388336734</v>
+        <v>7.590697381047192</v>
       </c>
       <c r="D5" t="n">
-        <v>45.30509338163123</v>
+        <v>7.362077674515075</v>
       </c>
       <c r="E5" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F5" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.31118502054213</v>
+        <v>4.600567565838096</v>
       </c>
       <c r="D6" t="n">
-        <v>27.36407793397664</v>
+        <v>4.446662664271204</v>
       </c>
       <c r="E6" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F6" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.72027294954145</v>
+        <v>5.967044354300486</v>
       </c>
       <c r="D7" t="n">
-        <v>37.77885834457417</v>
+        <v>6.139064480993302</v>
       </c>
       <c r="E7" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F7" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.51401761246272</v>
+        <v>5.121027862025191</v>
       </c>
       <c r="D8" t="n">
-        <v>33.57104393239145</v>
+        <v>5.455294639013611</v>
       </c>
       <c r="E8" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F8" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.63001253836233</v>
+        <v>1.239877037483879</v>
       </c>
       <c r="D9" t="n">
-        <v>6.64869714871471</v>
+        <v>1.08041328666614</v>
       </c>
       <c r="E9" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F9" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.09413148087196</v>
+        <v>2.452796365641694</v>
       </c>
       <c r="D10" t="n">
-        <v>16.37867378708368</v>
+        <v>2.661534490401099</v>
       </c>
       <c r="E10" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F10" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.5010236115422</v>
+        <v>1.706416336875608</v>
       </c>
       <c r="D11" t="n">
-        <v>11.67339706683872</v>
+        <v>1.896927023361292</v>
       </c>
       <c r="E11" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F11" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.53682460242966</v>
+        <v>2.03723399789482</v>
       </c>
       <c r="D12" t="n">
-        <v>12.4871896464958</v>
+        <v>2.029168317555568</v>
       </c>
       <c r="E12" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.75475322786628</v>
+        <v>1.26014739952827</v>
       </c>
       <c r="D13" t="n">
-        <v>6.413006109864138</v>
+        <v>1.042113492852923</v>
       </c>
       <c r="E13" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F13" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.13284594040272</v>
+        <v>3.596587465315442</v>
       </c>
       <c r="D14" t="n">
-        <v>22.98849328747434</v>
+        <v>3.735630159214581</v>
       </c>
       <c r="E14" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F14" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.36831060701437</v>
+        <v>5.747350473639835</v>
       </c>
       <c r="D15" t="n">
-        <v>35.52564851352802</v>
+        <v>5.772917883448303</v>
       </c>
       <c r="E15" t="n">
-        <v>14.99543624789548</v>
+        <v>2.436758390283016</v>
       </c>
       <c r="F15" t="n">
-        <v>15.1297267842162</v>
+        <v>2.458580602435132</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
